--- a/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,334 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 뭔가에 집중하는 게 힘들어져서 왔어요. 직장에서 대출 관련 서류나 고객 후속 목록을 보다가, 같은 줄을 계속 읽고도 여전히 머리에 안 들어온 걸 깨닫곤 해요. 그러다 전화 거는 것도 미루게 돼요, 간단한 결정조차 필요 이상으로 힘들게 느껴져서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 평소에 즐거워하시던 일들이 즐겁지 않게 느껴지거나, 예전에 좋아하시던 활동들에 흥미를 잃으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그 부분을 딱히 유심히 살펴본 적이 없어서요. 여전히 평소 하던 것들을 좀 하긴 하는데, 그게 예전보다 덜 즐거운 건지 아니면 그냥 정신이 딴 데 팔려서인지 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 요즘 유난히 피곤하거나 에너지가 별로 없다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 밤새 잤어도 피곤한 채로 깨요. 그리고 요즘엔 별로 많은 일을 하지 않아도—고객 전화 몇 통이나, 그냥 토마토에 물 주는 것만으로도—이미 하루를 꽉 채운 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 요즘 거의 매일, 하루 대부분 가라앉거나 우울한 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 대부분의 날에 이 둔한 무게감이 항상 함께 있어요. 커뮤니티 센터나 정원처럼 보통 좋아하던 곳에 있어도, 그냥 억지로 웃으면서 흘러가는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이 무거운 느낌, 피로감, 집중하기 어려운 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 이제 2년이 조금 넘었어요. 가까운 친구가 세상을 떠난 이후로 시작됐고, 그 이후로 제가 정말 예전의 저로 돌아왔다는 느낌이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이번 시기 전에, 2년 이상 가라앉거나 흥미를 잃었던 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 사람들처럼 힘든 시기는 있었지만, 이번처럼 이렇게 오래 지속된 건 기억이 안 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 몇 달 동안 식욕이나 체중에 눈에 띄는 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 큰 변화는 딱히 못 느꼈어요. 식욕이 좀 왔다 갔다 하긴 하는데, 체중은 제가 보기엔 비슷한 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 요즘 했던 일이나 하지 않은 일에 대해 무가치하거나 죄책감을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 모르겠어요... 딱히 명확하게 그런 건 아니에요. 가끔 스스로에게 답답함을 느끼긴 하는데, 특정한 일로 무가치감이나 심한 죄책감을 느꼈다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 앞서 말씀하신 평소의 어려움보다도 유난히 생각을 명확히 하거나 일에 집중하기 힘들었던 날들이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 사실 그게 제가 병원에 온 큰 이유예요. 직장에서 대출 관련 서류나 후속 연락 목록을 보다가, 같은 줄을 계속 읽고도 여전히 안 들어온다는 걸 깨닫곤 해요. 그러다 전화 거는 것도 미루게 돼요, 간단한 결정도 필요 이상으로 힘들게 느껴져서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 지금의 2년이라는 기간 이전에, 몇 주 이상 기분이 가라앉거나 힘들어하셨던 시기가 있었는지 떠올려 보실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나처럼 힘든 시기는 있었지만, 이번처럼 눈에 띄게 몇 주씩 가라앉았던 시기는 분명하게 짚을 수가 없어요. 지금은 구분하기가 좀 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 가라앉거나 기분이 힘들었던 시기들 사이에 두 달 이상 평소의 자신으로 돌아왔다고 느꼈던 때가 있었는지 떠올려 보실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 딱히 없어요. 2년이 조금 넘게 가까운 친구가 세상을 떠난 이후로, 두 달 정도 평소의 저로 돌아왔다고 느낀 적이 없는 것 같아요. 그 이후로 계속 이어지고 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 살면서 비정상적으로 들뜨거나, 지나치게 에너지가 넘치거나, 극도로 자신감이 넘쳤던 시기가 있었나요, 오래 지속되지 않았더라도요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 그렇게 비정상적으로 들뜨거나 지나치게 자신감 넘쳤던 시기는 기억이 안 나요. 저답지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 2년 전 가까운 친구가 세상을 떠나기 전에, 적어도 2주 이상 가라앉거나 흥미를 잃거나 평소처럼 기능하는 데 어려움을 겪었던 뚜렷한 시기가 있었는지 떠올려 보실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 그 전에는 그렇게 분명한 게 딱히 기억이 안 나요. 물론 스트레스받는 시기는 있었지만, 눈에 띄게 두 주 정도 가라앉아 있거나 평소처럼 기능하지 못했던 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 2년 전 친구분이 돌아가시기 전에, 적어도 2개월 연속으로 완전히 평소의 자신으로 느꼈던 때가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 그녀가 세상을 떠나기 전에는, 기본적으로 평소의 제 모습이었던 것 같아요, 네. 2년이 조금 넘은 그녀의 죽음 이후로는 계속 이 상태가 이어지고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 지금의 2년이라는 기간 이전에, 적어도 2개월 연속으로 완전히 평소의 자신으로 느꼈던 때가 있었는지 떠올려 보실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 딱히 없어요. 지금 이 시기는 가까운 친구가 2년이 조금 넘게 전에 세상을 떠난 후 시작됐고, 그 이후로 몇 달씩 완전히 평소의 저로 느낀 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>진단명: 지속성 우울장애 (D014)
 인구통계: 성별 여성 / 나이 62 / 직업상태 credit counselor or loan officer / 최종학력 전문학사
@@ -575,383 +894,34 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S031
-배경 서술: 라리사가 세이어 커뮤니티 센터에서 가장 가까이 지내던 친구, 예산관리 수업을 수채화 워크숍으로 바꾸는 걸 도와줬던 도예가 친구는 그들이 새로운 시니어 재무 교육 시리즈를 계획하던 바로 그 시기에 갑작스럽게 세상을 떠났다. 처음에 라리사는 이 상실을 또 하나의 정리해야 할 프로젝트처럼 대했지만, 그 후 2년 2개월에 걸쳐 슬픔은 그녀의 일상 속에 자리를 잡았고, 피로감 때문에 정원 가꾸기와 워크숍을 유지하기가 더 힘들어졌으며, 한때 믿음직했던 직장에서의 결단력도 눈에 띄게 흔들렸다. 그녀가 고객 후속 연락을 미루기 시작하고 늘 달력에 지켜오던 갤러리 행사나 걷기 모임 일정에서 물러나기 시작하면서 손상이 분명해졌다. 그녀는 1차 진료의가 지속되는 낮은 에너지와 집중력 문제에 대해 의학적 원인을 찾지 못하고 평가를 의뢰한 후 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 뭔가에 집중하는 게 힘들어져서 왔어요. 직장에서 대출 관련 서류나 고객 후속 목록을 보다가, 같은 줄을 계속 읽고도 여전히 머리에 안 들어온 걸 깨닫곤 해요. 그러다 전화 거는 것도 미루게 돼요, 간단한 결정조차 필요 이상으로 힘들게 느껴져서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 평소에 즐거워하시던 일들이 즐겁지 않게 느껴지거나, 예전에 좋아하시던 활동들에 흥미를 잃으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그 부분을 딱히 유심히 살펴본 적이 없어서요. 여전히 평소 하던 것들을 좀 하긴 하는데, 그게 예전보다 덜 즐거운 건지 아니면 그냥 정신이 딴 데 팔려서인지 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 요즘 유난히 피곤하거나 에너지가 별로 없다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 밤새 잤어도 피곤한 채로 깨요. 그리고 요즘엔 별로 많은 일을 하지 않아도—고객 전화 몇 통이나, 그냥 토마토에 물 주는 것만으로도—이미 하루를 꽉 채운 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 요즘 거의 매일, 하루 대부분 가라앉거나 우울한 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 대부분의 날에 이 둔한 무게감이 항상 함께 있어요. 커뮤니티 센터나 정원처럼 보통 좋아하던 곳에 있어도, 그냥 억지로 웃으면서 흘러가는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이 무거운 느낌, 피로감, 집중하기 어려운 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 이제 2년이 조금 넘었어요. 가까운 친구가 세상을 떠난 이후로 시작됐고, 그 이후로 제가 정말 예전의 저로 돌아왔다는 느낌이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이번 시기 전에, 2년 이상 가라앉거나 흥미를 잃었던 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 사람들처럼 힘든 시기는 있었지만, 이번처럼 이렇게 오래 지속된 건 기억이 안 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 몇 달 동안 식욕이나 체중에 눈에 띄는 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 큰 변화는 딱히 못 느꼈어요. 식욕이 좀 왔다 갔다 하긴 하는데, 체중은 제가 보기엔 비슷한 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 요즘 했던 일이나 하지 않은 일에 대해 무가치하거나 죄책감을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 모르겠어요... 딱히 명확하게 그런 건 아니에요. 가끔 스스로에게 답답함을 느끼긴 하는데, 특정한 일로 무가치감이나 심한 죄책감을 느꼈다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 앞서 말씀하신 평소의 어려움보다도 유난히 생각을 명확히 하거나 일에 집중하기 힘들었던 날들이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 사실 그게 제가 병원에 온 큰 이유예요. 직장에서 대출 관련 서류나 후속 연락 목록을 보다가, 같은 줄을 계속 읽고도 여전히 안 들어온다는 걸 깨닫곤 해요. 그러다 전화 거는 것도 미루게 돼요, 간단한 결정도 필요 이상으로 힘들게 느껴져서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 지금의 2년이라는 기간 이전에, 몇 주 이상 기분이 가라앉거나 힘들어하셨던 시기가 있었는지 떠올려 보실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나처럼 힘든 시기는 있었지만, 이번처럼 눈에 띄게 몇 주씩 가라앉았던 시기는 분명하게 짚을 수가 없어요. 지금은 구분하기가 좀 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 가라앉거나 기분이 힘들었던 시기들 사이에 두 달 이상 평소의 자신으로 돌아왔다고 느꼈던 때가 있었는지 떠올려 보실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 딱히 없어요. 2년이 조금 넘게 가까운 친구가 세상을 떠난 이후로, 두 달 정도 평소의 저로 돌아왔다고 느낀 적이 없는 것 같아요. 그 이후로 계속 이어지고 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 살면서 비정상적으로 들뜨거나, 지나치게 에너지가 넘치거나, 극도로 자신감이 넘쳤던 시기가 있었나요, 오래 지속되지 않았더라도요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 그렇게 비정상적으로 들뜨거나 지나치게 자신감 넘쳤던 시기는 기억이 안 나요. 저답지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 2년 전 가까운 친구가 세상을 떠나기 전에, 적어도 2주 이상 가라앉거나 흥미를 잃거나 평소처럼 기능하는 데 어려움을 겪었던 뚜렷한 시기가 있었는지 떠올려 보실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 그 전에는 그렇게 분명한 게 딱히 기억이 안 나요. 물론 스트레스받는 시기는 있었지만, 눈에 띄게 두 주 정도 가라앉아 있거나 평소처럼 기능하지 못했던 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 2년 전 친구분이 돌아가시기 전에, 적어도 2개월 연속으로 완전히 평소의 자신으로 느꼈던 때가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 그녀가 세상을 떠나기 전에는, 기본적으로 평소의 제 모습이었던 것 같아요, 네. 2년이 조금 넘은 그녀의 죽음 이후로는 계속 이 상태가 이어지고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 지금의 2년이라는 기간 이전에, 적어도 2개월 연속으로 완전히 평소의 자신으로 느꼈던 때가 있었는지 떠올려 보실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 딱히 없어요. 지금 이 시기는 가까운 친구가 2년이 조금 넘게 전에 세상을 떠난 후 시작됐고, 그 이후로 몇 달씩 완전히 평소의 저로 느낀 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+배경 서술: 라리사가 세이어 커뮤니티 센터에서 가장 가까이 지내던 친구, 예산관리 수업을 수채화 워크숍으로 바꾸는 걸 도와줬던 도예가 친구는 그들이 새로운 시니어 재무 교육 시리즈를 계획하던 바로 그 시기에 갑작스럽게 세상을 떠났다. 처음에 라리사는 이 상실을 또 하나의 정리해야 할 프로젝트처럼 대했지만, 그 후 2년 2개월에 걸쳐 슬픔은 그녀의 일상 속에 자리를 잡았고, 피로감 때문에 정원 가꾸기와 워크숍을 유지하기가 더 힘들어졌으며, 한때 믿음직했던 직장에서의 결단력도 눈에 띄게 흔들렸다. 그녀가 고객 후속 연락을 미루기 시작하고 늘 달력에 지켜오던 갤러리 행사나 걷기 모임 일정에서 물러나기 시작하면서 손상이 분명해졌다. 그녀는 1차 진료의가 지속되는 낮은 에너지와 집중력 문제에 대해 의학적 원인을 찾지 못하고 평가를 의뢰한 후 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S083 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
+        </is>
+      </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 낮은 자존감: 자신을 무능하거나 무가치하다고 평가하는 지속적인 경향, 만성적으로 낮은 자기평가.; 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.2)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
@@ -880,6 +880,11 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -917,11 +922,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S004_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0376</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0376</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4643</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
